--- a/data/fmsForecastOutput/File1/RPT_RPT5713512752455CZ_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT5713512752455CZ_fmsForecastOutput.xlsx
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>33.24301493444691</v>
+        <v>33.2430149344469</v>
       </c>
       <c r="D8" s="149" t="n">
         <v>12.38462060959148</v>
@@ -1884,13 +1884,13 @@
         <v>11.16597918764814</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>9.109498034422586</v>
+        <v>9.109498034422582</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>7.737317135895518</v>
+        <v>7.737317135895516</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>32.73593038944851</v>
+        <v>32.7359303894485</v>
       </c>
       <c r="I8" s="149" t="n">
         <v>12.08020833942218</v>
@@ -1899,25 +1899,25 @@
         <v>10.74536453089184</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>8.777883831876805</v>
+        <v>8.777883831876801</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>7.480316261491202</v>
+        <v>7.4803162614912</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>29966.17347643991</v>
+        <v>29966.1734764399</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>23852.46668286989</v>
+        <v>23852.46668286988</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>25213.05451676014</v>
+        <v>25213.05451676013</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>24301.92188076144</v>
+        <v>24301.92188076143</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>24510.74857133398</v>
+        <v>24510.74857133397</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>34.8181203802187</v>
+        <v>34.81812038021869</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>12.97142308236514</v>
+        <v>12.97142308236513</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>11.69504054566638</v>
+        <v>11.69504054566637</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>9.541120135804203</v>
+        <v>9.541120135804201</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>8.103923184728471</v>
+        <v>8.103923184728469</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>34.26224628437446</v>
+        <v>34.26224628437445</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>12.63786882320594</v>
+        <v>12.63786882320593</v>
       </c>
       <c r="AA8" s="149" t="n">
         <v>11.23444494365821</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>9.177963055026286</v>
+        <v>9.177963055026282</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>7.822434154386021</v>
+        <v>7.822434154386019</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>29966.17347643991</v>
+        <v>29966.1734764399</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>23852.46668286989</v>
+        <v>23852.46668286988</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>25213.05451676014</v>
+        <v>25213.05451676013</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>24301.92188076144</v>
+        <v>24301.92188076143</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>24510.74857133398</v>
+        <v>24510.74857133397</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>148.647768723232</v>
+        <v>148.6477687232319</v>
       </c>
       <c r="D9" s="156" t="n">
         <v>119.8607365928716</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>136.3692037973394</v>
+        <v>136.3692037973393</v>
       </c>
       <c r="F9" s="156" t="n">
         <v>143.1217395074897</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>142.5726311837514</v>
+        <v>142.5726311837513</v>
       </c>
       <c r="H9" s="155" t="n">
         <v>126.2506491287394</v>
@@ -2043,7 +2043,7 @@
         <v>93.80534373777257</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>99.19872792547044</v>
+        <v>99.19872792547042</v>
       </c>
       <c r="K9" s="156" t="n">
         <v>104.0536929654512</v>
@@ -2064,7 +2064,7 @@
         <v>27877.0159360097</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>30907.32170614858</v>
+        <v>30907.32170614857</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2084,22 +2084,22 @@
         <v>143.8145524251556</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>143.2627860192755</v>
+        <v>143.2627860192754</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>126.7693327954454</v>
+        <v>126.7693327954453</v>
       </c>
       <c r="Z9" s="156" t="n">
         <v>94.16034657816169</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>99.54757382350682</v>
+        <v>99.54757382350681</v>
       </c>
       <c r="AB9" s="156" t="n">
         <v>104.4194109129287</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>105.1968289844817</v>
+        <v>105.1968289844816</v>
       </c>
       <c r="AD9" s="158" t="n">
         <v>22415.88456682608</v>
@@ -2114,7 +2114,7 @@
         <v>27877.0159360097</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>30907.32170614858</v>
+        <v>30907.32170614857</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>49.78212053985676</v>
+        <v>49.78212053985675</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>21.38731608872115</v>
@@ -2182,37 +2182,37 @@
         <v>18.22822848242168</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>16.37338026002994</v>
+        <v>16.37338026002993</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>47.92759239537332</v>
+        <v>47.9275923953733</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>20.43982926559778</v>
+        <v>20.43982926559777</v>
       </c>
       <c r="J10" s="162" t="n">
         <v>19.11615207388863</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>17.18419223571833</v>
+        <v>17.18419223571832</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>15.51653852999624</v>
+        <v>15.51653852999623</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>52382.05804326598</v>
+        <v>52382.05804326596</v>
       </c>
       <c r="N10" s="165" t="n">
         <v>44957.25837037079</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>49542.86344087818</v>
+        <v>49542.86344087817</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>52178.93781677114</v>
+        <v>52178.93781677113</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>55418.07027748256</v>
+        <v>55418.07027748253</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>51.82642681736501</v>
+        <v>51.826426817365</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>22.32152251293537</v>
+        <v>22.32152251293536</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>21.23179796863111</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>19.03706997814685</v>
+        <v>19.03706997814684</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>17.1028008923212</v>
+        <v>17.10280089232119</v>
       </c>
       <c r="Y10" s="161" t="n">
         <v>49.81952878891892</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>21.29144800593416</v>
+        <v>21.29144800593415</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>19.90738701726304</v>
+        <v>19.90738701726303</v>
       </c>
       <c r="AB10" s="162" t="n">
         <v>17.90121077024454</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>16.17008990766155</v>
+        <v>16.17008990766154</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>52382.05804326598</v>
+        <v>52382.05804326596</v>
       </c>
       <c r="AE10" s="165" t="n">
         <v>44957.25837037079</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>49542.86344087818</v>
+        <v>49542.86344087817</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>52178.93781677114</v>
+        <v>52178.93781677113</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>55418.07027748256</v>
+        <v>55418.07027748253</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2339,7 +2339,7 @@
         <v>219.1307727146449</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>234.2963343895348</v>
+        <v>234.2963343895347</v>
       </c>
       <c r="K11" s="156" t="n">
         <v>250.2270693893988</v>
@@ -2354,7 +2354,7 @@
         <v>44733.12607788116</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>53353.20043519454</v>
+        <v>53353.20043519451</v>
       </c>
       <c r="P11" s="159" t="n">
         <v>63664.61716388016</v>
@@ -2374,7 +2374,7 @@
         <v>301.0610453624729</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>343.170077243958</v>
+        <v>343.1700772439578</v>
       </c>
       <c r="W11" s="156" t="n">
         <v>379.9623249641656</v>
@@ -2389,7 +2389,7 @@
         <v>253.332919551713</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>268.2698850830515</v>
+        <v>268.2698850830514</v>
       </c>
       <c r="AB11" s="156" t="n">
         <v>285.0465671319957</v>
@@ -2404,7 +2404,7 @@
         <v>44733.12607788116</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>53353.20043519454</v>
+        <v>53353.20043519451</v>
       </c>
       <c r="AG11" s="159" t="n">
         <v>63664.61716388016</v>
@@ -2461,37 +2461,37 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>78.74397133151601</v>
+        <v>78.74397133151598</v>
       </c>
       <c r="D12" s="162" t="n">
         <v>39.36900667916361</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>39.26213760819459</v>
+        <v>39.26213760819458</v>
       </c>
       <c r="F12" s="162" t="n">
         <v>37.84291271620291</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>34.68892655150318</v>
+        <v>34.68892655150317</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>75.1402144932151</v>
+        <v>75.14021449321508</v>
       </c>
       <c r="I12" s="162" t="n">
         <v>37.3145272613032</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>36.49583093868577</v>
+        <v>36.49583093868576</v>
       </c>
       <c r="K12" s="162" t="n">
         <v>35.20142114117247</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>32.40950127072383</v>
+        <v>32.40950127072382</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>93515.7414689015</v>
+        <v>93515.74146890148</v>
       </c>
       <c r="N12" s="165" t="n">
         <v>89690.38444825193</v>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>83.13197116729432</v>
+        <v>83.13197116729431</v>
       </c>
       <c r="U12" s="162" t="n">
         <v>41.47222311718629</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>41.34199722459471</v>
+        <v>41.34199722459469</v>
       </c>
       <c r="W12" s="162" t="n">
         <v>39.8297601193493</v>
@@ -2526,22 +2526,22 @@
         <v>36.49876268635376</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>79.12560309163763</v>
+        <v>79.12560309163761</v>
       </c>
       <c r="Z12" s="162" t="n">
         <v>39.19870494964348</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>38.28625009656045</v>
+        <v>38.28625009656044</v>
       </c>
       <c r="AB12" s="162" t="n">
         <v>36.91430186725892</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>33.9839041308846</v>
+        <v>33.98390413088459</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>93515.7414689015</v>
+        <v>93515.74146890148</v>
       </c>
       <c r="AE12" s="165" t="n">
         <v>89690.38444825193</v>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>85.31427063764373</v>
+        <v>85.3142706376437</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>106.4336657728856</v>
+        <v>106.4336657728855</v>
       </c>
       <c r="E13" s="156" t="n">
         <v>116.6269781502456</v>
@@ -2615,13 +2615,13 @@
         <v>123.4247459404469</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>131.1011686181123</v>
+        <v>131.1011686181122</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>85.31427063764373</v>
+        <v>85.3142706376437</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>106.4336657728856</v>
+        <v>106.4336657728855</v>
       </c>
       <c r="J13" s="156" t="n">
         <v>116.6269781502456</v>
@@ -2630,19 +2630,19 @@
         <v>123.4247459404469</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>131.1011686181123</v>
+        <v>131.1011686181122</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>736.4368637819756</v>
+        <v>736.4368637819754</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>805.1896113223746</v>
+        <v>805.1896113223743</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>898.5758174492481</v>
+        <v>898.5758174492478</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>975.4712887117287</v>
+        <v>975.4712887117283</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>1066.629990298585</v>
@@ -2656,43 +2656,43 @@
         <v>24.29836821958207</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>30.31338582139146</v>
+        <v>30.31338582139145</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>33.21654440988009</v>
+        <v>33.21654440988007</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>35.15261751468424</v>
+        <v>35.15261751468423</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>37.3389404292092</v>
+        <v>37.33894042920918</v>
       </c>
       <c r="Y13" s="155" t="n">
         <v>24.29836821958207</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>30.31338582139146</v>
+        <v>30.31338582139145</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>33.21654440988009</v>
+        <v>33.21654440988007</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>35.15261751468424</v>
+        <v>35.15261751468423</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>37.3389404292092</v>
+        <v>37.33894042920918</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>736.4368637819756</v>
+        <v>736.4368637819754</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>805.1896113223746</v>
+        <v>805.1896113223743</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>898.5758174492481</v>
+        <v>898.5758174492478</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>975.4712887117287</v>
+        <v>975.4712887117283</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>1066.629990298585</v>
@@ -2746,19 +2746,19 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>78.79138311795599</v>
+        <v>78.79138311795596</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>39.59097023290599</v>
+        <v>39.59097023290598</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>39.48891492530741</v>
+        <v>39.4889149253074</v>
       </c>
       <c r="F14" s="168" t="n">
         <v>38.06330008066629</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>34.90606458836059</v>
+        <v>34.90606458836058</v>
       </c>
       <c r="H14" s="167" t="n">
         <v>75.21029445561352</v>
@@ -2767,28 +2767,28 @@
         <v>37.53138991504643</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>36.71421269678084</v>
+        <v>36.71421269678083</v>
       </c>
       <c r="K14" s="168" t="n">
         <v>35.41279060193204</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>32.61719815176764</v>
+        <v>32.61719815176762</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>94252.17833268347</v>
+        <v>94252.17833268346</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>90495.57405957433</v>
+        <v>90495.57405957431</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>103794.639693522</v>
+        <v>103794.6396935219</v>
       </c>
       <c r="P14" s="171" t="n">
         <v>116819.026269363</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>126096.8945017437</v>
+        <v>126096.8945017436</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2799,46 +2799,46 @@
         <v>81.58842016735795</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>41.33683127297982</v>
+        <v>41.33683127297981</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>41.2546305860612</v>
+        <v>41.25463058606118</v>
       </c>
       <c r="W14" s="168" t="n">
         <v>39.78555736836314</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>36.50571099967004</v>
+        <v>36.50571099967002</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>77.75475194982047</v>
+        <v>77.75475194982045</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>39.09674022381645</v>
+        <v>39.09674022381644</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>38.23572845333935</v>
+        <v>38.23572845333934</v>
       </c>
       <c r="AB14" s="168" t="n">
         <v>36.89886055189966</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>34.00975339094192</v>
+        <v>34.00975339094191</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>94252.17833268347</v>
+        <v>94252.17833268346</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>90495.57405957433</v>
+        <v>90495.57405957431</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>103794.639693522</v>
+        <v>103794.6396935219</v>
       </c>
       <c r="AG14" s="171" t="n">
         <v>116819.026269363</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>126096.8945017437</v>
+        <v>126096.8945017436</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="C19" s="74" t="n">
-        <v>901.4276694075818</v>
+        <v>901.4276694075817</v>
       </c>
       <c r="D19" s="75" t="n">
         <v>1925.974758112246</v>
@@ -3182,7 +3182,7 @@
         <v>108.83806653774</v>
       </c>
       <c r="M19" s="74" t="n">
-        <v>915.3909212276018</v>
+        <v>915.3909212276017</v>
       </c>
       <c r="N19" s="75" t="n">
         <v>1974.507890317626</v>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="T19" s="74" t="n">
-        <v>860.6487986486675</v>
+        <v>860.6487986486674</v>
       </c>
       <c r="U19" s="75" t="n">
         <v>1838.847328578597</v>
@@ -3232,7 +3232,7 @@
         <v>108.83806653774</v>
       </c>
       <c r="AD19" s="74" t="n">
-        <v>874.6120504686875</v>
+        <v>874.6120504686874</v>
       </c>
       <c r="AE19" s="75" t="n">
         <v>1887.380460783977</v>
@@ -3715,10 +3715,10 @@
         <v>3061.169097881079</v>
       </c>
       <c r="G23" s="87" t="n">
-        <v>3604.327863124007</v>
+        <v>3604.327863124008</v>
       </c>
       <c r="H23" s="85" t="n">
-        <v>56.95743939234</v>
+        <v>56.95743939234001</v>
       </c>
       <c r="I23" s="86" t="n">
         <v>125.43400213578</v>
@@ -3745,7 +3745,7 @@
         <v>3290.877221009629</v>
       </c>
       <c r="Q23" s="87" t="n">
-        <v>3857.827476795747</v>
+        <v>3857.827476795748</v>
       </c>
       <c r="S23" s="42" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>3425.602823467538</v>
       </c>
       <c r="Y23" s="85" t="n">
-        <v>56.95743939234</v>
+        <v>56.95743939234001</v>
       </c>
       <c r="Z23" s="86" t="n">
         <v>125.43400213578</v>
@@ -3954,10 +3954,10 @@
         <v>3069.072466701319</v>
       </c>
       <c r="G25" s="93" t="n">
-        <v>3612.463793577881</v>
+        <v>3612.463793577882</v>
       </c>
       <c r="H25" s="91" t="n">
-        <v>56.95743939234</v>
+        <v>56.95743939234001</v>
       </c>
       <c r="I25" s="92" t="n">
         <v>125.43400213578</v>
@@ -3984,7 +3984,7 @@
         <v>3298.780589829869</v>
       </c>
       <c r="Q25" s="93" t="n">
-        <v>3865.963407249621</v>
+        <v>3865.963407249622</v>
       </c>
       <c r="S25" s="51" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>3454.168979283363</v>
       </c>
       <c r="Y25" s="91" t="n">
-        <v>56.95743939234</v>
+        <v>56.95743939234001</v>
       </c>
       <c r="Z25" s="92" t="n">
         <v>125.43400213578</v>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>29.06346128541952</v>
+        <v>29.06346128541951</v>
       </c>
       <c r="D35" s="149" t="n">
         <v>12.93325813107621</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>11.75360713701505</v>
+        <v>11.75360713701504</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>9.716298370749909</v>
+        <v>9.716298370749906</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>8.273045295813482</v>
+        <v>8.27304529581348</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>28.62013109797842</v>
+        <v>28.62013109797841</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>12.61536042613422</v>
+        <v>12.61536042613421</v>
       </c>
       <c r="J35" s="149" t="n">
         <v>11.31085694480147</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>9.362594739250378</v>
+        <v>9.362594739250374</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>7.99824980305196</v>
+        <v>7.998249803051958</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>26198.6081714332</v>
+        <v>26198.60817143319</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>24909.12870060275</v>
+        <v>24909.12870060274</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>26539.93282039779</v>
+        <v>26539.93282039778</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>25920.71737475279</v>
+        <v>25920.71737475278</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>26207.86114920854</v>
+        <v>26207.86114920853</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>30.44053301714762</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>13.54605589788531</v>
+        <v>13.5460558978853</v>
       </c>
       <c r="V35" s="149" t="n">
         <v>12.31051121582623</v>
@@ -4470,37 +4470,37 @@
         <v>10.17667161026175</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>8.665034973171226</v>
+        <v>8.665034973171224</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>29.95454745609082</v>
+        <v>29.95454745609081</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>13.19772521659784</v>
+        <v>13.19772521659783</v>
       </c>
       <c r="AA35" s="149" t="n">
         <v>11.82567601561114</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>9.789323971681085</v>
+        <v>9.789323971681084</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>8.364055776196878</v>
+        <v>8.364055776196876</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>26198.6081714332</v>
+        <v>26198.60817143319</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>24909.12870060275</v>
+        <v>24909.12870060274</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>26539.93282039779</v>
+        <v>26539.93282039778</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>25920.71737475279</v>
+        <v>25920.71737475278</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>26207.86114920854</v>
+        <v>26207.86114920853</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4522,7 +4522,7 @@
         <v>152.3124872651066</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>152.1157564838712</v>
+        <v>152.1157564838711</v>
       </c>
       <c r="H36" s="155" t="n">
         <v>125.2960999358579</v>
@@ -4552,7 +4552,7 @@
         <v>29667.1745980313</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>32976.10897116543</v>
+        <v>32976.10897116541</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>153.0497900610495</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>152.8521069602922</v>
+        <v>152.8521069602921</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>125.8108619666845</v>
@@ -4602,7 +4602,7 @@
         <v>29667.1745980313</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>32976.10897116543</v>
+        <v>32976.10897116541</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>46.04048623845072</v>
+        <v>46.04048623845071</v>
       </c>
       <c r="D37" s="162" t="n">
         <v>22.33265031143399</v>
@@ -4624,13 +4624,13 @@
         <v>19.41911503247201</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>17.486022938494</v>
+        <v>17.48602293849399</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>44.3253448063667</v>
+        <v>44.32534480636669</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>21.34328391278312</v>
+        <v>21.34328391278311</v>
       </c>
       <c r="J37" s="162" t="n">
         <v>20.10509087017041</v>
@@ -4639,22 +4639,22 @@
         <v>18.30686981388951</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>16.57095507174425</v>
+        <v>16.57095507174424</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>48445.01191048809</v>
+        <v>48445.01191048807</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>46944.40040916394</v>
+        <v>46944.40040916392</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>52105.87191382804</v>
+        <v>52105.87191382803</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>55587.89197278409</v>
+        <v>55587.89197278408</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>59183.97012037397</v>
+        <v>59183.97012037394</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>47.93114204049598</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>23.30814930832186</v>
+        <v>23.30814930832185</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>22.33018579505337</v>
@@ -4674,10 +4674,10 @@
         <v>20.28079975754941</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>18.26501088756106</v>
+        <v>18.26501088756105</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>46.07508287590758</v>
+        <v>46.07508287590757</v>
       </c>
       <c r="Z37" s="162" t="n">
         <v>22.23254479281594</v>
@@ -4689,22 +4689,22 @@
         <v>19.07073260043547</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>17.2689181190716</v>
+        <v>17.26891811907159</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>48445.01191048809</v>
+        <v>48445.01191048807</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>46944.40040916394</v>
+        <v>46944.40040916392</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>52105.87191382804</v>
+        <v>52105.87191382803</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>55587.89197278409</v>
+        <v>55587.89197278408</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>59183.97012037397</v>
+        <v>59183.97012037394</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4720,7 +4720,7 @@
         <v>265.5809127461571</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>304.7626318059581</v>
+        <v>304.7626318059579</v>
       </c>
       <c r="F38" s="156" t="n">
         <v>341.7608589849468</v>
@@ -4735,7 +4735,7 @@
         <v>229.1618792055127</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>246.6689628544317</v>
+        <v>246.6689628544316</v>
       </c>
       <c r="K38" s="156" t="n">
         <v>266.8165636938714</v>
@@ -4750,7 +4750,7 @@
         <v>46780.86563448362</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>56170.65521150504</v>
+        <v>56170.65521150502</v>
       </c>
       <c r="P38" s="159" t="n">
         <v>67885.43870174915</v>
@@ -4770,7 +4770,7 @@
         <v>314.8426579076703</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>361.2920674025847</v>
+        <v>361.2920674025846</v>
       </c>
       <c r="W38" s="156" t="n">
         <v>405.1529761646477</v>
@@ -4785,7 +4785,7 @@
         <v>264.929691023764</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>282.436575420318</v>
+        <v>282.4365754203179</v>
       </c>
       <c r="AB38" s="156" t="n">
         <v>303.9445161567947</v>
@@ -4800,7 +4800,7 @@
         <v>46780.86563448362</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>56170.65521150504</v>
+        <v>56170.65521150502</v>
       </c>
       <c r="AG38" s="159" t="n">
         <v>67885.43870174915</v>
@@ -4816,43 +4816,43 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>75.86677992454088</v>
+        <v>75.86677992454085</v>
       </c>
       <c r="D39" s="162" t="n">
         <v>41.14009152238239</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>41.3151654941079</v>
+        <v>41.31516549410789</v>
       </c>
       <c r="F39" s="162" t="n">
         <v>40.33535120944499</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>37.06577904015178</v>
+        <v>37.06577904015177</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>72.39469917563017</v>
+        <v>72.39469917563015</v>
       </c>
       <c r="I39" s="162" t="n">
         <v>38.99318769088791</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>38.40420789422528</v>
+        <v>38.40420789422526</v>
       </c>
       <c r="K39" s="162" t="n">
         <v>37.51988372165767</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>34.63016969172004</v>
+        <v>34.63016969172003</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>90098.81083635232</v>
+        <v>90098.81083635231</v>
       </c>
       <c r="N39" s="165" t="n">
         <v>93725.26604364754</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>108276.5271253331</v>
+        <v>108276.527125333</v>
       </c>
       <c r="P39" s="165" t="n">
         <v>123473.3306745332</v>
@@ -4866,28 +4866,28 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>80.09444856025618</v>
+        <v>80.09444856025617</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>43.33792489564418</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>43.50378153721778</v>
+        <v>43.50378153721776</v>
       </c>
       <c r="W39" s="162" t="n">
         <v>42.45305785656496</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>38.99962343783457</v>
+        <v>38.99962343783456</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>76.23446740928136</v>
+        <v>76.23446740928135</v>
       </c>
       <c r="Z39" s="162" t="n">
         <v>40.9621284664187</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>40.28824855827651</v>
+        <v>40.28824855827649</v>
       </c>
       <c r="AB39" s="162" t="n">
         <v>39.34557949155555</v>
@@ -4896,13 +4896,13 @@
         <v>36.31244914906384</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>90098.81083635232</v>
+        <v>90098.81083635231</v>
       </c>
       <c r="AE39" s="165" t="n">
         <v>93725.26604364754</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>108276.5271253331</v>
+        <v>108276.527125333</v>
       </c>
       <c r="AG39" s="165" t="n">
         <v>123473.3306745332</v>
@@ -4918,46 +4918,46 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>79.66361321140545</v>
+        <v>79.66361321140543</v>
       </c>
       <c r="D40" s="156" t="n">
         <v>101.9262551993843</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>112.8247865600319</v>
+        <v>112.8247865600318</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>121.1482847990558</v>
+        <v>121.1482847990557</v>
       </c>
       <c r="G40" s="157" t="n">
         <v>129.3107001526823</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>79.66361321140545</v>
+        <v>79.66361321140543</v>
       </c>
       <c r="I40" s="156" t="n">
         <v>101.9262551993843</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>112.8247865600319</v>
+        <v>112.8247865600318</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>121.1482847990558</v>
+        <v>121.1482847990557</v>
       </c>
       <c r="L40" s="157" t="n">
         <v>129.3107001526823</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>687.6601186702486</v>
+        <v>687.6601186702484</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687163</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>869.2810738962293</v>
+        <v>869.2810738962289</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063707</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>1052.062863383992</v>
@@ -4968,46 +4968,46 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>22.68900376274206</v>
+        <v>22.68900376274205</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>29.02962964539426</v>
+        <v>29.02962964539425</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>32.13364174178123</v>
+        <v>32.13364174178122</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>34.504258328845</v>
+        <v>34.50425832884499</v>
       </c>
       <c r="X40" s="157" t="n">
         <v>36.82899687892851</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>22.68900376274206</v>
+        <v>22.68900376274205</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>29.02962964539426</v>
+        <v>29.02962964539425</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>32.13364174178123</v>
+        <v>32.13364174178122</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>34.504258328845</v>
+        <v>34.50425832884499</v>
       </c>
       <c r="AC40" s="157" t="n">
         <v>36.82899687892851</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>687.6601186702486</v>
+        <v>687.6601186702484</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687163</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>869.2810738962293</v>
+        <v>869.2810738962289</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063707</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>1052.062863383992</v>
@@ -5020,19 +5020,19 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>75.89417816631916</v>
+        <v>75.89417816631914</v>
       </c>
       <c r="D41" s="180" t="n">
         <v>41.34127517246636</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>41.52477957589833</v>
+        <v>41.52477957589831</v>
       </c>
       <c r="F41" s="180" t="n">
         <v>40.54345786920423</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>37.27353150655127</v>
+        <v>37.27353150655126</v>
       </c>
       <c r="H41" s="179" t="n">
         <v>72.44476821545784</v>
@@ -5041,16 +5041,16 @@
         <v>39.1906414254394</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>38.60702661544716</v>
+        <v>38.60702661544715</v>
       </c>
       <c r="K41" s="180" t="n">
         <v>37.72024445483262</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>34.82942512433014</v>
+        <v>34.82942512433012</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>90786.47095502257</v>
+        <v>90786.47095502255</v>
       </c>
       <c r="N41" s="183" t="n">
         <v>94496.35629231625</v>
@@ -5070,37 +5070,37 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>78.58836653774696</v>
+        <v>78.58836653774695</v>
       </c>
       <c r="U41" s="186" t="n">
         <v>43.16432020637139</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>43.38152731751639</v>
+        <v>43.38152731751637</v>
       </c>
       <c r="W41" s="186" t="n">
         <v>42.37793532217563</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>38.98167224411141</v>
+        <v>38.9816722441114</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>74.89566452873706</v>
+        <v>74.89566452873703</v>
       </c>
       <c r="Z41" s="186" t="n">
         <v>40.82519540265867</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>40.20698464244926</v>
+        <v>40.20698464244924</v>
       </c>
       <c r="AB41" s="186" t="n">
         <v>39.30314489382545</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>36.31642895000012</v>
+        <v>36.31642895000011</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>90786.47095502257</v>
+        <v>90786.47095502255</v>
       </c>
       <c r="AE41" s="189" t="n">
         <v>94496.35629231625</v>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="C46" s="148" t="n">
-        <v>4.799645254128303</v>
+        <v>4.799645254128301</v>
       </c>
       <c r="D46" s="149" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="148" t="n">
-        <v>4.726432101391022</v>
+        <v>4.72643210139102</v>
       </c>
       <c r="I46" s="149" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="151" t="n">
-        <v>4326.533035412037</v>
+        <v>4326.533035412035</v>
       </c>
       <c r="N46" s="152" t="n">
         <v>0</v>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="T46" s="148" t="n">
-        <v>5.027059867166801</v>
+        <v>5.027059867166799</v>
       </c>
       <c r="U46" s="149" t="n">
         <v>0</v>
@@ -5436,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="Y46" s="148" t="n">
-        <v>4.946802451548127</v>
+        <v>4.946802451548125</v>
       </c>
       <c r="Z46" s="149" t="n">
         <v>0</v>
@@ -5451,7 +5451,7 @@
         <v>0</v>
       </c>
       <c r="AD46" s="151" t="n">
-        <v>4326.533035412037</v>
+        <v>4326.533035412035</v>
       </c>
       <c r="AE46" s="152" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="155" t="n">
-        <v>2.873833781895743</v>
+        <v>2.873833781895742</v>
       </c>
       <c r="I47" s="156" t="n">
         <v>0</v>
@@ -5503,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="158" t="n">
-        <v>510.2510503017755</v>
+        <v>510.2510503017754</v>
       </c>
       <c r="N47" s="159" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="T47" s="155" t="n">
-        <v>3.400037041403212</v>
+        <v>3.400037041403211</v>
       </c>
       <c r="U47" s="156" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="Y47" s="155" t="n">
-        <v>2.885640538168158</v>
+        <v>2.885640538168157</v>
       </c>
       <c r="Z47" s="156" t="n">
         <v>0</v>
@@ -5553,7 +5553,7 @@
         <v>0</v>
       </c>
       <c r="AD47" s="158" t="n">
-        <v>510.2510503017755</v>
+        <v>510.2510503017754</v>
       </c>
       <c r="AE47" s="159" t="n">
         <v>0</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="C48" s="161" t="n">
-        <v>4.596714550264224</v>
+        <v>4.596714550264223</v>
       </c>
       <c r="D48" s="162" t="n">
         <v>0</v>
@@ -5590,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="161" t="n">
-        <v>4.425473622534028</v>
+        <v>4.425473622534026</v>
       </c>
       <c r="I48" s="162" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="164" t="n">
-        <v>4836.784085713813</v>
+        <v>4836.784085713811</v>
       </c>
       <c r="N48" s="165" t="n">
         <v>0</v>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="T48" s="161" t="n">
-        <v>4.785478956221884</v>
+        <v>4.785478956221882</v>
       </c>
       <c r="U48" s="162" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="Y48" s="161" t="n">
-        <v>4.600168702897724</v>
+        <v>4.600168702897722</v>
       </c>
       <c r="Z48" s="162" t="n">
         <v>0</v>
@@ -5655,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="AD48" s="164" t="n">
-        <v>4836.784085713813</v>
+        <v>4836.784085713811</v>
       </c>
       <c r="AE48" s="165" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="C50" s="161" t="n">
-        <v>4.399410777542743</v>
+        <v>4.399410777542741</v>
       </c>
       <c r="D50" s="162" t="n">
         <v>0</v>
@@ -5794,7 +5794,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="161" t="n">
-        <v>4.19806956492703</v>
+        <v>4.198069564927028</v>
       </c>
       <c r="I50" s="162" t="n">
         <v>0</v>
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="164" t="n">
-        <v>5224.706779851274</v>
+        <v>5224.706779851273</v>
       </c>
       <c r="N50" s="165" t="n">
         <v>0</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="T50" s="161" t="n">
-        <v>4.644567498024944</v>
+        <v>4.644567498024943</v>
       </c>
       <c r="U50" s="162" t="n">
         <v>0</v>
@@ -5844,7 +5844,7 @@
         <v>0</v>
       </c>
       <c r="Y50" s="161" t="n">
-        <v>4.420732471764428</v>
+        <v>4.420732471764426</v>
       </c>
       <c r="Z50" s="162" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="AD50" s="164" t="n">
-        <v>5224.706779851274</v>
+        <v>5224.706779851273</v>
       </c>
       <c r="AE50" s="165" t="n">
         <v>0</v>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="C52" s="179" t="n">
-        <v>4.367664290125944</v>
+        <v>4.367664290125942</v>
       </c>
       <c r="D52" s="180" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="179" t="n">
-        <v>4.169152822864703</v>
+        <v>4.169152822864702</v>
       </c>
       <c r="I52" s="180" t="n">
         <v>0</v>
@@ -6013,7 +6013,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="182" t="n">
-        <v>5224.706779851274</v>
+        <v>5224.706779851273</v>
       </c>
       <c r="N52" s="183" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="T52" s="185" t="n">
-        <v>4.522713209885905</v>
+        <v>4.522713209885903</v>
       </c>
       <c r="U52" s="186" t="n">
         <v>0</v>
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="Y52" s="185" t="n">
-        <v>4.310200431060052</v>
+        <v>4.310200431060049</v>
       </c>
       <c r="Z52" s="186" t="n">
         <v>0</v>
@@ -6063,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="AD52" s="188" t="n">
-        <v>5224.706779851274</v>
+        <v>5224.706779851273</v>
       </c>
       <c r="AE52" s="189" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>9.772854192859578</v>
+        <v>9.772854192859572</v>
       </c>
       <c r="N57" s="152" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>9.772854192859578</v>
+        <v>9.772854192859572</v>
       </c>
       <c r="AE57" s="152" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>0.3712528407756716</v>
+        <v>0.3712528407756715</v>
       </c>
       <c r="D58" s="156" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>0.3153152754420838</v>
+        <v>0.3153152754420837</v>
       </c>
       <c r="I58" s="156" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>55.984431488026</v>
+        <v>55.98443148802599</v>
       </c>
       <c r="N58" s="159" t="n">
         <v>0</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>0.3730499735152165</v>
+        <v>0.3730499735152164</v>
       </c>
       <c r="U58" s="156" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>0.3166107054803716</v>
+        <v>0.3166107054803715</v>
       </c>
       <c r="Z58" s="156" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>55.984431488026</v>
+        <v>55.98443148802599</v>
       </c>
       <c r="AE58" s="159" t="n">
         <v>0</v>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.062493480485929</v>
+        <v>0.06249348048592899</v>
       </c>
       <c r="D59" s="162" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.06016541737509602</v>
+        <v>0.06016541737509599</v>
       </c>
       <c r="I59" s="162" t="n">
         <v>0</v>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="N59" s="165" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.06505977965268386</v>
+        <v>0.06505977965268384</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0</v>
@@ -6603,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.06254044055226261</v>
+        <v>0.06254044055226259</v>
       </c>
       <c r="Z59" s="162" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="AE59" s="165" t="n">
         <v>0</v>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.05537024822944803</v>
+        <v>0.05537024822944799</v>
       </c>
       <c r="D61" s="162" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.05283620140248251</v>
+        <v>0.05283620140248248</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0</v>
@@ -6772,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="N61" s="165" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.05845574971012558</v>
+        <v>0.05845574971012555</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.05563859950679487</v>
+        <v>0.05563859950679485</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="AE61" s="165" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.05497069224853028</v>
+        <v>0.05497069224853025</v>
       </c>
       <c r="D63" s="180" t="n">
         <v>0</v>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.05247226012331142</v>
+        <v>0.0524722601233114</v>
       </c>
       <c r="I63" s="180" t="n">
         <v>0</v>
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="N63" s="183" t="n">
         <v>0</v>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.05692211202015977</v>
+        <v>0.05692211202015975</v>
       </c>
       <c r="U63" s="186" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.05424746172935661</v>
+        <v>0.05424746172935657</v>
       </c>
       <c r="Z63" s="186" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="AE63" s="189" t="n">
         <v>0</v>
@@ -7297,16 +7297,16 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.147141945442066</v>
+        <v>0.1471419454420659</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.03663247190347484</v>
+        <v>0.03663247190347481</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.01431807736221278</v>
+        <v>0.01431807736221277</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.005411602615854708</v>
+        <v>0.005411602615854703</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>0.005002985281895763</v>
@@ -7315,28 +7315,28 @@
         <v>0.1448974617030969</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.03573205078557531</v>
+        <v>0.03573205078557529</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.01377872536326053</v>
+        <v>0.01377872536326052</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.0052146033652736</v>
+        <v>0.005214603365273595</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.00483680732001359</v>
+        <v>0.004836807320013589</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>132.6378209519391</v>
+        <v>132.637820951939</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>70.55321621334859</v>
+        <v>70.55321621334855</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>32.3305694056821</v>
+        <v>32.33056940568208</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>14.43683763070941</v>
+        <v>14.43683763070939</v>
       </c>
       <c r="Q68" s="153" t="n">
         <v>15.8487641383771</v>
@@ -7350,43 +7350,43 @@
         <v>0.1541137583183733</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.03836817506099608</v>
+        <v>0.03836817506099605</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.01499649000531014</v>
+        <v>0.01499649000531013</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.005668012714860292</v>
+        <v>0.005668012714860287</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.005240034459840948</v>
+        <v>0.005240034459840947</v>
       </c>
       <c r="Y68" s="148" t="n">
         <v>0.151653319755726</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.03738155484773976</v>
+        <v>0.03738155484773974</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.01440587064704167</v>
+        <v>0.01440587064704166</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.005452275052820332</v>
+        <v>0.005452275052820327</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.005058022342322208</v>
+        <v>0.005058022342322206</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>132.6378209519391</v>
+        <v>132.637820951939</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>70.55321621334859</v>
+        <v>70.55321621334855</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>32.3305694056821</v>
+        <v>32.33056940568208</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>14.43683763070941</v>
+        <v>14.43683763070939</v>
       </c>
       <c r="AH68" s="153" t="n">
         <v>15.8487641383771</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>0.845066219028563</v>
+        <v>0.8450662190285628</v>
       </c>
       <c r="D69" s="156" t="n">
         <v>0.3798975964538547</v>
@@ -7408,13 +7408,13 @@
         <v>0.4220668701846503</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>0.4236427786325573</v>
+        <v>0.4236427786325572</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>0.4165487326267489</v>
+        <v>0.4165487326267492</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>0.7177380436013975</v>
+        <v>0.7177380436013974</v>
       </c>
       <c r="I69" s="156" t="n">
         <v>0.297315247957744</v>
@@ -7423,13 +7423,13 @@
         <v>0.307023106800737</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>0.3080006976337506</v>
+        <v>0.3080006976337505</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>0.3062607452808094</v>
+        <v>0.3062607452808096</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>127.4348547561338</v>
+        <v>127.4348547561337</v>
       </c>
       <c r="N69" s="159" t="n">
         <v>66.89145973609607</v>
@@ -7438,10 +7438,10 @@
         <v>75.30150517013892</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>82.5164404216678</v>
+        <v>82.51644042166778</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>90.30068098406994</v>
+        <v>90.30068098407001</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>0.8491569518189886</v>
+        <v>0.8491569518189884</v>
       </c>
       <c r="U69" s="156" t="n">
         <v>0.3817365760744151</v>
@@ -7458,13 +7458,13 @@
         <v>0.4241099796436953</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>0.4256935166303102</v>
+        <v>0.4256935166303101</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>0.4185651303018627</v>
+        <v>0.418565130301863</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>0.7206867729961266</v>
+        <v>0.7206867729961265</v>
       </c>
       <c r="Z69" s="156" t="n">
         <v>0.2984404264743437</v>
@@ -7473,13 +7473,13 @@
         <v>0.3081027955593498</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>0.3090832289668543</v>
+        <v>0.3090832289668542</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>0.3073493518778005</v>
+        <v>0.3073493518778008</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>127.4348547561338</v>
+        <v>127.4348547561337</v>
       </c>
       <c r="AE69" s="159" t="n">
         <v>66.89145973609607</v>
@@ -7488,10 +7488,10 @@
         <v>75.30150517013892</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>82.5164404216678</v>
+        <v>82.51644042166778</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>90.30068098406994</v>
+        <v>90.30068098407001</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7504,46 +7504,46 @@
         <v>0.2471641965752578</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.06538594291105521</v>
+        <v>0.06538594291105518</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.04417603539932981</v>
+        <v>0.0441760353993298</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.03386972940431258</v>
+        <v>0.03386972940431257</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.03136206693373802</v>
+        <v>0.03136206693373803</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.2379566145380389</v>
+        <v>0.2379566145380388</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.06248925783525023</v>
+        <v>0.06248925783525021</v>
       </c>
       <c r="J70" s="162" t="n">
         <v>0.04152991899781572</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.03192981378397475</v>
+        <v>0.03192981378397474</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.02972084641224702</v>
+        <v>0.02972084641224704</v>
       </c>
       <c r="M70" s="164" t="n">
         <v>260.0726757080728</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>137.4446759494447</v>
+        <v>137.4446759494446</v>
       </c>
       <c r="O70" s="165" t="n">
         <v>107.632074575821</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>96.9532780523772</v>
+        <v>96.95327805237717</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>106.149445122447</v>
+        <v>106.1494451224471</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7554,46 +7554,46 @@
         <v>0.2573140116726188</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.0682420267538065</v>
+        <v>0.06824202675380647</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.04612616840497183</v>
+        <v>0.04612616840497182</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.03537263148926336</v>
+        <v>0.03537263148926335</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.03275922123721513</v>
+        <v>0.03275922123721515</v>
       </c>
       <c r="Y70" s="161" t="n">
         <v>0.2473499255021189</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.06509285213883773</v>
+        <v>0.0650928521388377</v>
       </c>
       <c r="AA70" s="162" t="n">
         <v>0.04324888016633795</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.0332621003397253</v>
+        <v>0.03326210033972529</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.03097267845459028</v>
+        <v>0.0309726784545903</v>
       </c>
       <c r="AD70" s="164" t="n">
         <v>260.0726757080728</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>137.4446759494447</v>
+        <v>137.4446759494446</v>
       </c>
       <c r="AF70" s="165" t="n">
         <v>107.632074575821</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>96.9532780523772</v>
+        <v>96.95327805237717</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>106.149445122447</v>
+        <v>106.1494451224471</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.3839130617067616</v>
+        <v>0.3839130617067615</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.3756597890879749</v>
+        <v>0.3756597890879748</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.3190001249957816</v>
+        <v>0.3190001249957817</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.2898236696578317</v>
+        <v>0.2898236696578319</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.2896500274801809</v>
+        <v>0.289650027480181</v>
       </c>
       <c r="H71" s="155" t="n">
         <v>0.3427834229845441</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.3241456711598434</v>
+        <v>0.3241456711598433</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.258192513684695</v>
+        <v>0.2581925136846951</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.2262686132195626</v>
+        <v>0.2262686132195627</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.2222703138770042</v>
+        <v>0.2222703138770043</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>51.96879991723807</v>
+        <v>51.96879991723806</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>66.17075728781755</v>
+        <v>66.17075728781752</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>58.79476078607205</v>
+        <v>58.79476078607207</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>57.56892998018631</v>
+        <v>57.56892998018633</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>63.63131279334116</v>
+        <v>63.63131279334119</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.4551238547355932</v>
+        <v>0.4551238547355931</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.445339709252898</v>
+        <v>0.4453397092528978</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>0.3781704271893471</v>
+        <v>0.3781704271893472</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.3435821254475552</v>
+        <v>0.3435821254475554</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.3433762749435745</v>
+        <v>0.3433762749435746</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.3984473868040612</v>
+        <v>0.3984473868040611</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.3747386467801407</v>
+        <v>0.3747386467801406</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.2956310697560413</v>
+        <v>0.2956310697560414</v>
       </c>
       <c r="AB71" s="156" t="n">
         <v>0.2577542533880874</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.2525991700201997</v>
+        <v>0.2525991700201998</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>51.96879991723807</v>
+        <v>51.96879991723806</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>66.17075728781755</v>
+        <v>66.17075728781752</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>58.79476078607205</v>
+        <v>58.79476078607207</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>57.56892998018631</v>
+        <v>57.56892998018633</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>63.63131279334116</v>
+        <v>63.63131279334119</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,10 +7705,10 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.2627513253376129</v>
+        <v>0.2627513253376128</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.08937566050598865</v>
+        <v>0.08937566050598862</v>
       </c>
       <c r="E72" s="162" t="n">
         <v>0.06350362750070619</v>
@@ -7717,13 +7717,13 @@
         <v>0.05047816801088276</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.04710469312540086</v>
+        <v>0.04710469312540088</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.2507263808314286</v>
+        <v>0.2507263808314285</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.08471157394511497</v>
+        <v>0.08471157394511494</v>
       </c>
       <c r="J72" s="162" t="n">
         <v>0.05902932938565546</v>
@@ -7732,10 +7732,10 @@
         <v>0.04695471682931904</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.04400942212605254</v>
+        <v>0.04400942212605256</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>312.0414756253109</v>
+        <v>312.0414756253108</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>203.6154332372622</v>
@@ -7747,7 +7747,7 @@
         <v>154.5222080325635</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>169.7807579157882</v>
+        <v>169.7807579157883</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,37 +7755,37 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.2773931163590232</v>
+        <v>0.2773931163590231</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.09415039002525837</v>
+        <v>0.09415039002525835</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.06686764786178982</v>
+        <v>0.06686764786178984</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>0.053128397864492</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.04956230090443732</v>
+        <v>0.04956230090443734</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.2640247466429814</v>
+        <v>0.2640247466429813</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.08898904090734812</v>
+        <v>0.08898904090734809</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.06192520103702655</v>
+        <v>0.06192520103702656</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.04923950610340085</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.04614733099081712</v>
+        <v>0.04614733099081714</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>312.0414756253109</v>
+        <v>312.0414756253108</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>203.6154332372622</v>
@@ -7797,7 +7797,7 @@
         <v>154.5222080325635</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>169.7807579157882</v>
+        <v>169.7807579157883</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>7.825390701591194</v>
+        <v>7.82539070159119</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>9.546277323050761</v>
+        <v>9.546277323050758</v>
       </c>
       <c r="E73" s="156" t="n">
         <v>10.05861667760935</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>10.44461166199181</v>
+        <v>10.4446116619918</v>
       </c>
       <c r="G73" s="157" t="n">
         <v>10.810665665364</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>7.825390701591194</v>
+        <v>7.82539070159119</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>9.546277323050761</v>
+        <v>9.546277323050758</v>
       </c>
       <c r="J73" s="156" t="n">
         <v>10.05861667760935</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>10.44461166199181</v>
+        <v>10.4446116619918</v>
       </c>
       <c r="L73" s="157" t="n">
         <v>10.810665665364</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>67.54914673800951</v>
+        <v>67.54914673800948</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121332</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>82.5476181488975</v>
+        <v>82.54761814889747</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>87.95482401348623</v>
+        <v>87.9548240134862</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>2.228750516275973</v>
+        <v>2.228750516275972</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>2.718876452767622</v>
+        <v>2.718876452767621</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>2.864795889192536</v>
+        <v>2.864795889192535</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>2.974731169554628</v>
+        <v>2.974731169554627</v>
       </c>
       <c r="X73" s="157" t="n">
         <v>3.078987056591012</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>2.228750516275973</v>
+        <v>2.228750516275972</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>2.718876452767622</v>
+        <v>2.718876452767621</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>2.864795889192536</v>
+        <v>2.864795889192535</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>2.974731169554628</v>
+        <v>2.974731169554627</v>
       </c>
       <c r="AC73" s="157" t="n">
         <v>3.078987056591012</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>67.54914673800951</v>
+        <v>67.54914673800948</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121332</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>82.5476181488975</v>
+        <v>82.54761814889747</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>87.95482401348623</v>
+        <v>87.9548240134862</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.3173239142446481</v>
+        <v>0.3173239142446479</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>0.1206751188015574</v>
@@ -7921,10 +7921,10 @@
         <v>0.07724477957220309</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.07134620487753211</v>
+        <v>0.07134620487753213</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.3029014605876229</v>
+        <v>0.3029014605876228</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>0.1143974221935446</v>
@@ -7933,16 +7933,16 @@
         <v>0.08628124753884053</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.07186589702641837</v>
+        <v>0.07186589702641835</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>0.06666787933014512</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>379.5906223633204</v>
+        <v>379.5906223633203</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>275.8347190384756</v>
+        <v>275.8347190384754</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>243.925454007809</v>
@@ -7951,7 +7951,7 @@
         <v>237.069826181461</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>257.7355819292744</v>
+        <v>257.7355819292745</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,25 +7959,25 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.3285886834323496</v>
+        <v>0.3285886834323495</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.1259965844585626</v>
+        <v>0.1259965844585625</v>
       </c>
       <c r="V74" s="186" t="n">
         <v>0.09695158175164875</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.0807398886214139</v>
+        <v>0.08073988862141389</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.07461580005930887</v>
+        <v>0.0746158000593089</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.3131489924843802</v>
+        <v>0.31314899248438</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.119168682745272</v>
+        <v>0.1191686827452719</v>
       </c>
       <c r="AA74" s="186" t="n">
         <v>0.08985692758160997</v>
@@ -7986,13 +7986,13 @@
         <v>0.07488169296294647</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.06951419078258363</v>
+        <v>0.06951419078258364</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>379.5906223633204</v>
+        <v>379.5906223633203</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>275.8347190384756</v>
+        <v>275.8347190384754</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>243.925454007809</v>
@@ -8001,7 +8001,7 @@
         <v>237.069826181461</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>257.7355819292744</v>
+        <v>257.7355819292745</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8263,40 +8263,40 @@
         <v>34.02109001396057</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>12.96989060297969</v>
+        <v>12.96989060297968</v>
       </c>
       <c r="E79" s="149" t="n">
         <v>11.76792521437726</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>9.721709973365764</v>
+        <v>9.72170997336576</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>8.278048281095378</v>
+        <v>8.278048281095376</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>33.50213681479684</v>
+        <v>33.50213681479683</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>12.6510924769198</v>
+        <v>12.65109247691979</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>11.32463567016474</v>
+        <v>11.32463567016473</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>9.367809342615651</v>
+        <v>9.367809342615649</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>8.003086610371973</v>
+        <v>8.003086610371971</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>30667.55188199004</v>
+        <v>30667.55188199002</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>24979.6819168161</v>
+        <v>24979.68191681609</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>26572.26338980347</v>
+        <v>26572.26338980346</v>
       </c>
       <c r="P79" s="152" t="n">
         <v>25935.1542123835</v>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>35.63306186000858</v>
+        <v>35.63306186000857</v>
       </c>
       <c r="U79" s="149" t="n">
         <v>13.5844240729463</v>
@@ -8322,10 +8322,10 @@
         <v>10.18233962297661</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>8.670275007631068</v>
+        <v>8.670275007631066</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>35.06417715781059</v>
+        <v>35.06417715781058</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>13.23510677144558</v>
@@ -8334,19 +8334,19 @@
         <v>11.84008188625818</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>9.794776246733907</v>
+        <v>9.794776246733903</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>8.369113798539201</v>
+        <v>8.369113798539198</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>30667.55188199004</v>
+        <v>30667.55188199002</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>24979.6819168161</v>
+        <v>24979.68191681609</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>26572.26338980347</v>
+        <v>26572.26338980346</v>
       </c>
       <c r="AG79" s="152" t="n">
         <v>25935.1542123835</v>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>152.1238573261689</v>
+        <v>152.1238573261688</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>125.5251222980276</v>
@@ -8392,7 +8392,7 @@
         <v>112.1469201944818</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>22940.07407560083</v>
+        <v>22940.07407560082</v>
       </c>
       <c r="N80" s="159" t="n">
         <v>22102.16316829728</v>
@@ -8404,7 +8404,7 @@
         <v>29749.69103845297</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>33066.4096521495</v>
+        <v>33066.40965214949</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>152.8602470165361</v>
+        <v>152.860247016536</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>126.1327548388207</v>
@@ -8424,7 +8424,7 @@
         <v>153.4754835776798</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>153.2706720905941</v>
+        <v>153.270672090594</v>
       </c>
       <c r="Y80" s="155" t="n">
         <v>129.7337999833292</v>
@@ -8442,7 +8442,7 @@
         <v>112.5455474395243</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>22940.07407560083</v>
+        <v>22940.07407560082</v>
       </c>
       <c r="AE80" s="159" t="n">
         <v>22102.16316829728</v>
@@ -8454,7 +8454,7 @@
         <v>29749.69103845297</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>33066.4096521495</v>
+        <v>33066.40965214949</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8467,19 +8467,19 @@
         <v>50.94685846577613</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>22.39803625434505</v>
+        <v>22.39803625434504</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>21.43028097902091</v>
+        <v>21.4302809790209</v>
       </c>
       <c r="F81" s="162" t="n">
         <v>19.45298476187632</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>17.51738500542774</v>
+        <v>17.51738500542773</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>49.04894046081387</v>
+        <v>49.04894046081385</v>
       </c>
       <c r="I81" s="162" t="n">
         <v>21.40577317061837</v>
@@ -8488,25 +8488,25 @@
         <v>20.14662078916822</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>18.33879962767349</v>
+        <v>18.33879962767348</v>
       </c>
       <c r="L81" s="163" t="n">
         <v>16.60067591815649</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>53607.62595759086</v>
+        <v>53607.62595759085</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>47081.84508511338</v>
+        <v>47081.84508511337</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>52213.50398840386</v>
+        <v>52213.50398840385</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>55684.84525083647</v>
+        <v>55684.84525083646</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>59290.11956549641</v>
+        <v>59290.1195654964</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,22 +8514,22 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>53.03899478804318</v>
+        <v>53.03899478804317</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>23.37639133507566</v>
+        <v>23.37639133507565</v>
       </c>
       <c r="V81" s="162" t="n">
         <v>22.37631196345834</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>20.31617238903868</v>
+        <v>20.31617238903867</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>18.29777010879828</v>
+        <v>18.29777010879827</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>50.98514194485969</v>
+        <v>50.98514194485968</v>
       </c>
       <c r="Z81" s="162" t="n">
         <v>22.29763764495478</v>
@@ -8541,22 +8541,22 @@
         <v>19.1039947007752</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>17.29989079752619</v>
+        <v>17.29989079752618</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>53607.62595759086</v>
+        <v>53607.62595759085</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>47081.84508511338</v>
+        <v>47081.84508511337</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>52213.50398840386</v>
+        <v>52213.50398840385</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>55684.84525083647</v>
+        <v>55684.84525083646</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>59290.11956549641</v>
+        <v>59290.1195654964</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8572,7 +8572,7 @@
         <v>265.9565725352451</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>305.0816319309538</v>
+        <v>305.0816319309537</v>
       </c>
       <c r="F82" s="156" t="n">
         <v>342.0506826546047</v>
@@ -8587,7 +8587,7 @@
         <v>229.4860248766726</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>246.9271553681164</v>
+        <v>246.9271553681163</v>
       </c>
       <c r="K82" s="156" t="n">
         <v>267.042832307091</v>
@@ -8602,7 +8602,7 @@
         <v>46847.03639177143</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>56229.44997229111</v>
+        <v>56229.44997229109</v>
       </c>
       <c r="P82" s="159" t="n">
         <v>67943.00763172934</v>
@@ -8622,7 +8622,7 @@
         <v>315.2879976169232</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>361.670237829774</v>
+        <v>361.6702378297739</v>
       </c>
       <c r="W82" s="156" t="n">
         <v>405.4965582900953</v>
@@ -8637,7 +8637,7 @@
         <v>265.3044296705441</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>282.7322064900741</v>
+        <v>282.732206490074</v>
       </c>
       <c r="AB82" s="156" t="n">
         <v>304.2022704101828</v>
@@ -8652,7 +8652,7 @@
         <v>46847.03639177143</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>56229.44997229111</v>
+        <v>56229.44997229109</v>
       </c>
       <c r="AG82" s="159" t="n">
         <v>67943.00763172934</v>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>80.58431227565069</v>
+        <v>80.58431227565065</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>41.22946718288838</v>
@@ -8680,31 +8680,31 @@
         <v>40.38582937745588</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>37.11288373327719</v>
+        <v>37.11288373327717</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>76.8963313227911</v>
+        <v>76.89633132279108</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>39.07789926483304</v>
+        <v>39.07789926483303</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>38.46323722361093</v>
+        <v>38.46323722361092</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>37.566838438487</v>
+        <v>37.56683843848699</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>34.67417911384609</v>
+        <v>34.67417911384608</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>95701.31637750979</v>
+        <v>95701.31637750976</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>93928.88147688482</v>
+        <v>93928.88147688481</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>108442.953960695</v>
+        <v>108442.9539606949</v>
       </c>
       <c r="P83" s="165" t="n">
         <v>123627.8528825658</v>
@@ -8718,43 +8718,43 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>85.07486492435028</v>
+        <v>85.07486492435025</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>43.43207528566944</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>43.57064918507957</v>
+        <v>43.57064918507955</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>42.50618625442946</v>
+        <v>42.50618625442945</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>39.04918573873901</v>
+        <v>39.049185738739</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>80.97486322719557</v>
+        <v>80.97486322719554</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>41.05111750732606</v>
+        <v>41.05111750732605</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>40.35017375931353</v>
+        <v>40.35017375931352</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>39.39481899765895</v>
+        <v>39.39481899765894</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>36.35859648005466</v>
+        <v>36.35859648005465</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>95701.31637750979</v>
+        <v>95701.31637750976</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>93928.88147688482</v>
+        <v>93928.88147688481</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>108442.953960695</v>
+        <v>108442.9539606949</v>
       </c>
       <c r="AG83" s="165" t="n">
         <v>123627.8528825658</v>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>87.48900391299664</v>
+        <v>87.48900391299662</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>111.4725325224351</v>
+        <v>111.472532522435</v>
       </c>
       <c r="E84" s="156" t="n">
         <v>122.8834032376412</v>
@@ -8785,34 +8785,34 @@
         <v>140.1213658180463</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>87.48900391299665</v>
+        <v>87.48900391299661</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>111.4725325224351</v>
+        <v>111.472532522435</v>
       </c>
       <c r="J84" s="156" t="n">
         <v>122.8834032376412</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>131.5928964610476</v>
+        <v>131.5928964610475</v>
       </c>
       <c r="L84" s="157" t="n">
         <v>140.1213658180463</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>755.2092654082581</v>
+        <v>755.2092654082578</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699296</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>946.7796925421452</v>
+        <v>946.7796925421449</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>1140.017687397479</v>
+        <v>1140.017687397478</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>24.91775427901804</v>
+        <v>24.91775427901802</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>31.74850609816189</v>
+        <v>31.74850609816187</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>34.99843763097377</v>
+        <v>34.99843763097375</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>37.47898949839963</v>
+        <v>37.47898949839961</v>
       </c>
       <c r="X84" s="157" t="n">
         <v>39.90798393551952</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>24.91775427901804</v>
+        <v>24.91775427901802</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>31.74850609816189</v>
+        <v>31.74850609816187</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>34.99843763097377</v>
+        <v>34.99843763097375</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>37.47898949839963</v>
+        <v>37.47898949839961</v>
       </c>
       <c r="AC84" s="157" t="n">
         <v>39.90798393551952</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>755.2092654082581</v>
+        <v>755.2092654082578</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699296</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>946.7796925421452</v>
+        <v>946.7796925421449</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>1140.017687397479</v>
+        <v>1140.017687397478</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,40 +8872,40 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>80.63413706293828</v>
+        <v>80.63413706293825</v>
       </c>
       <c r="D85" s="180" t="n">
         <v>41.46195029126793</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>41.61758158889122</v>
+        <v>41.61758158889121</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>40.62070264877643</v>
+        <v>40.62070264877642</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>37.3448777114288</v>
+        <v>37.34487771142879</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>76.96929475903349</v>
+        <v>76.96929475903346</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>39.30503884763296</v>
+        <v>39.30503884763295</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>38.693307862986</v>
+        <v>38.69330786298599</v>
       </c>
       <c r="K85" s="180" t="n">
         <v>37.79211035185904</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>34.89609300366028</v>
+        <v>34.89609300366027</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>96456.52564291804</v>
+        <v>96456.52564291802</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>94772.19101135475</v>
+        <v>94772.19101135473</v>
       </c>
       <c r="O85" s="183" t="n">
         <v>109389.7336532371</v>
@@ -8914,7 +8914,7 @@
         <v>124667.8800774211</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>134907.0186081302</v>
+        <v>134907.0186081301</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,40 +8922,40 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>83.49659054308538</v>
+        <v>83.49659054308535</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>43.29031679082996</v>
+        <v>43.29031679082995</v>
       </c>
       <c r="V85" s="186" t="n">
         <v>43.47847889926803</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>42.45867521079705</v>
+        <v>42.45867521079704</v>
       </c>
       <c r="X85" s="187" t="n">
         <v>39.05628804417071</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>79.57326141401084</v>
+        <v>79.5732614140108</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>40.94436408540395</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>40.29684157003086</v>
+        <v>40.29684157003085</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>39.3780265867884</v>
+        <v>39.37802658678839</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>36.3859431407827</v>
+        <v>36.38594314078269</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>96456.52564291804</v>
+        <v>96456.52564291802</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>94772.19101135475</v>
+        <v>94772.19101135473</v>
       </c>
       <c r="AF85" s="189" t="n">
         <v>109389.7336532371</v>
@@ -8964,7 +8964,7 @@
         <v>124667.8800774211</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>134907.0186081302</v>
+        <v>134907.0186081301</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="C90" s="74" t="n">
-        <v>901.4276694075818</v>
+        <v>901.4276694075817</v>
       </c>
       <c r="D90" s="75" t="n">
         <v>1925.974758112246</v>
@@ -9311,7 +9311,7 @@
         <v>108.83806653774</v>
       </c>
       <c r="M90" s="74" t="n">
-        <v>915.3909212276018</v>
+        <v>915.3909212276017</v>
       </c>
       <c r="N90" s="75" t="n">
         <v>1974.507890317626</v>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="T90" s="74" t="n">
-        <v>860.6487986486675</v>
+        <v>860.6487986486674</v>
       </c>
       <c r="U90" s="75" t="n">
         <v>1838.847328578597</v>
@@ -9361,7 +9361,7 @@
         <v>108.83806653774</v>
       </c>
       <c r="AD90" s="74" t="n">
-        <v>874.6120504686875</v>
+        <v>874.6120504686874</v>
       </c>
       <c r="AE90" s="75" t="n">
         <v>1887.380460783977</v>
@@ -9768,10 +9768,10 @@
         <v>3061.169097881079</v>
       </c>
       <c r="G94" s="87" t="n">
-        <v>3604.327863124007</v>
+        <v>3604.327863124008</v>
       </c>
       <c r="H94" s="85" t="n">
-        <v>56.95743939234</v>
+        <v>56.95743939234001</v>
       </c>
       <c r="I94" s="86" t="n">
         <v>125.43400213578</v>
@@ -9798,7 +9798,7 @@
         <v>3290.877221009629</v>
       </c>
       <c r="Q94" s="87" t="n">
-        <v>3857.827476795747</v>
+        <v>3857.827476795748</v>
       </c>
       <c r="S94" s="42" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>3425.602823467538</v>
       </c>
       <c r="Y94" s="85" t="n">
-        <v>56.95743939234</v>
+        <v>56.95743939234001</v>
       </c>
       <c r="Z94" s="86" t="n">
         <v>125.43400213578</v>
@@ -10000,10 +10000,10 @@
         <v>3069.072466701319</v>
       </c>
       <c r="G96" s="134" t="n">
-        <v>3612.463793577881</v>
+        <v>3612.463793577882</v>
       </c>
       <c r="H96" s="132" t="n">
-        <v>56.95743939234</v>
+        <v>56.95743939234001</v>
       </c>
       <c r="I96" s="133" t="n">
         <v>125.43400213578</v>
@@ -10030,7 +10030,7 @@
         <v>3298.780589829869</v>
       </c>
       <c r="Q96" s="134" t="n">
-        <v>3865.963407249621</v>
+        <v>3865.963407249622</v>
       </c>
       <c r="S96" s="51" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>3454.168979283363</v>
       </c>
       <c r="Y96" s="135" t="n">
-        <v>56.95743939234</v>
+        <v>56.95743939234001</v>
       </c>
       <c r="Z96" s="136" t="n">
         <v>125.43400213578</v>
